--- a/data/trans_orig/IP29B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses con lactancia materna exclusiva</t>
+          <t>Meses con lactancia materna exclusiva (tasa de respuesta: 97,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +571,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,64</t>
+          <t>5,54; 11,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,01</t>
+          <t>5,75; 6,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,68</t>
+          <t>5,84; 8,63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +621,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,91; 13,37</t>
+          <t>7,98; 13,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,05</t>
+          <t>7,34; 13,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,47</t>
+          <t>8,26; 12,57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,82</t>
+          <t>6,33; 10,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 12,8</t>
+          <t>7,28; 12,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 10,57</t>
+          <t>7,34; 10,68</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 15,71</t>
+          <t>9,54; 15,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,26</t>
+          <t>6,33; 10,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,26</t>
+          <t>8,43; 12,21</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,85</t>
+          <t>5,72; 11,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 15,43</t>
+          <t>6,15; 14,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,66</t>
+          <t>6,48; 11,42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +821,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,6; 10,98</t>
+          <t>6,44; 11,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 11,41</t>
+          <t>7,76; 11,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,64; 10,32</t>
+          <t>7,67; 10,4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,16; 12,63</t>
+          <t>9,14; 12,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,03</t>
+          <t>8,77; 12,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,31; 11,69</t>
+          <t>9,34; 11,85</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,89</t>
+          <t>5,0; 9,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,59</t>
+          <t>5,02; 8,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,09</t>
+          <t>5,47; 8,11</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,98; 9,63</t>
+          <t>8,0; 9,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,89; 9,47</t>
+          <t>7,99; 9,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,19; 9,31</t>
+          <t>8,22; 9,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP29B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Provincia-trans_orig.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 11,87</t>
+          <t>5,44; 10,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 6,92</t>
+          <t>5,77; 6,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 8,63</t>
+          <t>5,84; 8,5</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 13,1</t>
+          <t>7,82; 13,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 13,83</t>
+          <t>7,35; 13,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 12,57</t>
+          <t>8,27; 12,79</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,1</t>
+          <t>6,29; 9,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 12,68</t>
+          <t>7,27; 13,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 10,68</t>
+          <t>7,25; 10,57</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 15,79</t>
+          <t>9,57; 15,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,49</t>
+          <t>6,12; 10,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 12,21</t>
+          <t>8,69; 12,54</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,34</t>
+          <t>5,7; 11,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 14,15</t>
+          <t>6,27; 15,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 11,42</t>
+          <t>6,34; 11,3</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,2</t>
+          <t>6,51; 10,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,24</t>
+          <t>7,86; 11,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,4</t>
+          <t>7,67; 10,44</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,14; 12,67</t>
+          <t>9,02; 12,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,15</t>
+          <t>8,82; 11,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 11,85</t>
+          <t>9,28; 11,7</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,04</t>
+          <t>4,98; 8,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,73</t>
+          <t>4,64; 8,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,11</t>
+          <t>5,49; 8,05</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,0; 9,6</t>
+          <t>7,99; 9,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,99; 9,5</t>
+          <t>8,02; 9,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,22; 9,32</t>
+          <t>8,17; 9,32</t>
         </is>
       </c>
     </row>
